--- a/artfynd/A 18369-2026 artfynd.xlsx
+++ b/artfynd/A 18369-2026 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>591084</v>
+        <v>57028967</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,19 +713,20 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skidtjärnsberget, 2 km nordöst om Rengsjö, Hls</t>
+          <t>Glössbovägen Söderala hälsingland, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591834.5509325977</v>
+        <v>591950</v>
       </c>
       <c r="R2" t="n">
-        <v>6803397.227158946</v>
+        <v>6803998</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tallskog, ca 100-140 år</t>
+          <t>2011-08-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,42 +764,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Torr-frisk hed med tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Göran Vesslén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57028967</v>
+        <v>591084</v>
       </c>
       <c r="B3" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,26 +799,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1593</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,20 +826,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Glössbovägen Söderala hälsingland, Hls</t>
+          <t>Skidtjärnsberget, 2 km nordöst om Rengsjö, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591949.9505822576</v>
+        <v>591835</v>
       </c>
       <c r="R3" t="n">
-        <v>6803997.717425497</v>
+        <v>6803397</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,22 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tallskog, ca 100-140 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,27 +881,30 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Torr-frisk hed med tall</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18369-2026 artfynd.xlsx
+++ b/artfynd/A 18369-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57028967</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,8 +915,17 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/591084</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>